--- a/docs/oc-regiones/alimentos/antofagasta.xlsx
+++ b/docs/oc-regiones/alimentos/antofagasta.xlsx
@@ -1932,7 +1932,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4107,7 +4111,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10961,7 +10969,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21156,7 +21168,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22900,7 +22916,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24880,7 +24900,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24941,7 +24965,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26449,7 +26477,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27819,7 +27851,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31746,7 +31782,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32177,7 +32217,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35844,7 +35888,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36600,7 +36648,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44905,7 +44957,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48970,7 +49026,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K778" t="inlineStr"/>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L778" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53628,7 +53688,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K852" t="inlineStr"/>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L852" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58209,7 +58273,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K925" t="inlineStr"/>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L925" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59721,7 +59789,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K949" t="inlineStr"/>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L949" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60099,7 +60171,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K955" t="inlineStr"/>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L955" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61875,7 +61951,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K983" t="inlineStr"/>
+      <c r="K983" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L983" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63298,7 +63378,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1006" t="inlineStr"/>
+      <c r="K1006" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1006" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63481,7 +63565,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1009" t="inlineStr"/>
+      <c r="K1009" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1009" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64034,7 +64122,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1018" t="inlineStr"/>
+      <c r="K1018" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1018" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64916,7 +65008,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1032" t="inlineStr"/>
+      <c r="K1032" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1032" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65546,7 +65642,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1042" t="inlineStr"/>
+      <c r="K1042" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1042" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65912,7 +66012,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1048" t="inlineStr"/>
+      <c r="K1048" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1048" t="inlineStr">
         <is>
           <t>USD</t>
